--- a/data/trans_orig/P23_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275047</t>
+          <t>274201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>327757</t>
+          <t>331213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136854</t>
+          <t>137479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181816</t>
+          <t>181664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426836</t>
+          <t>426574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>494661</t>
+          <t>494209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366255</t>
+          <t>362799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418965</t>
+          <t>419811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>506535</t>
+          <t>506687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551497</t>
+          <t>550872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887702</t>
+          <t>888154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>955527</t>
+          <t>955789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>355472</t>
+          <t>353568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>416893</t>
+          <t>417826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194065</t>
+          <t>195716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247876</t>
+          <t>249589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>570411</t>
+          <t>569447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>654488</t>
+          <t>652858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>543865</t>
+          <t>542932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>605286</t>
+          <t>607190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>720517</t>
+          <t>718804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>774328</t>
+          <t>772677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1274663</t>
+          <t>1276293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358740</t>
+          <t>1359704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221242</t>
+          <t>221083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271059</t>
+          <t>272965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141004</t>
+          <t>142014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185290</t>
+          <t>186162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374130</t>
+          <t>376414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>445127</t>
+          <t>443487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407450</t>
+          <t>405544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457267</t>
+          <t>457426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>498551</t>
+          <t>497679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>542837</t>
+          <t>541827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>917223</t>
+          <t>918863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>988220</t>
+          <t>985936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>346130</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>406158</t>
+          <t>403481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>256471</t>
+          <t>257874</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316218</t>
+          <t>316263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614911</t>
+          <t>617821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>699192</t>
+          <t>702468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>536064</t>
+          <t>538741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596092</t>
+          <t>596603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>722394</t>
+          <t>722349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>782141</t>
+          <t>780738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1281642</t>
+          <t>1278366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1365923</t>
+          <t>1363013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1244842</t>
+          <t>1252736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1361477</t>
+          <t>1365380</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>785050</t>
+          <t>781070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>885840</t>
+          <t>876985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2055957</t>
+          <t>2058038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2216426</t>
+          <t>2217789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1914024</t>
+          <t>1910121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2030659</t>
+          <t>2022765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2493357</t>
+          <t>2502212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2594147</t>
+          <t>2598127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4438272</t>
+          <t>4436909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4598741</t>
+          <t>4596660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>233231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285479</t>
+          <t>286717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>139298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184324</t>
+          <t>185614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387643</t>
+          <t>385859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>460146</t>
+          <t>456953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417990</t>
+          <t>416752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469606</t>
+          <t>470238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>512726</t>
+          <t>511436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>558996</t>
+          <t>557752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940373</t>
+          <t>943566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1012876</t>
+          <t>1014660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>345319</t>
+          <t>347623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411719</t>
+          <t>411421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260104</t>
+          <t>258600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>319449</t>
+          <t>318886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>623222</t>
+          <t>623267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>712663</t>
+          <t>712581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>605199</t>
+          <t>605497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671599</t>
+          <t>669295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>712735</t>
+          <t>713298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>772080</t>
+          <t>773584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336439</t>
+          <t>1336521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1425880</t>
+          <t>1425835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252541</t>
+          <t>253889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>310962</t>
+          <t>307706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198306</t>
+          <t>195859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251946</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462691</t>
+          <t>462627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>541492</t>
+          <t>538756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446661</t>
+          <t>449917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505082</t>
+          <t>503734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524232</t>
+          <t>528158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577872</t>
+          <t>580319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>992309</t>
+          <t>995045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1071110</t>
+          <t>1071174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>310744</t>
+          <t>311519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>370497</t>
+          <t>373556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260235</t>
+          <t>258001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>319279</t>
+          <t>317420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>586676</t>
+          <t>586123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>670061</t>
+          <t>672261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>577242</t>
+          <t>574183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636995</t>
+          <t>636220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>731636</t>
+          <t>733495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>790680</t>
+          <t>792914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1328593</t>
+          <t>1326393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1411978</t>
+          <t>1412531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1206177</t>
+          <t>1203028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1328041</t>
+          <t>1319774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>902400</t>
+          <t>905512</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1013655</t>
+          <t>1012153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2136501</t>
+          <t>2142650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2303716</t>
+          <t>2302854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2097708</t>
+          <t>2105975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2219572</t>
+          <t>2222721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2542672</t>
+          <t>2544174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2653927</t>
+          <t>2650815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4678360</t>
+          <t>4679222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4845575</t>
+          <t>4839426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225737</t>
+          <t>226604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273338</t>
+          <t>274142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146785</t>
+          <t>146763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191230</t>
+          <t>192002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>383813</t>
+          <t>381533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>456358</t>
+          <t>453962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401462</t>
+          <t>400658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449063</t>
+          <t>448196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>480500</t>
+          <t>479728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>524945</t>
+          <t>524967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>890172</t>
+          <t>892568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>962717</t>
+          <t>964997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>307130</t>
+          <t>304565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366063</t>
+          <t>366431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>243123</t>
+          <t>244246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302717</t>
+          <t>300278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>562031</t>
+          <t>562462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>647181</t>
+          <t>645876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655296</t>
+          <t>654928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>714229</t>
+          <t>716794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739268</t>
+          <t>741707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>798862</t>
+          <t>797739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1416163</t>
+          <t>1417468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1501313</t>
+          <t>1500882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>282430</t>
+          <t>278434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338898</t>
+          <t>334659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197697</t>
+          <t>201555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251590</t>
+          <t>252319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>495680</t>
+          <t>497149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570007</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419790</t>
+          <t>424029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476258</t>
+          <t>480254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531305</t>
+          <t>530576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585198</t>
+          <t>581340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971575</t>
+          <t>965103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1045902</t>
+          <t>1044433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252683</t>
+          <t>257545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309222</t>
+          <t>314330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>230990</t>
+          <t>229682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288153</t>
+          <t>286428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>498984</t>
+          <t>500583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>577710</t>
+          <t>580701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>628345</t>
+          <t>623237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>684884</t>
+          <t>680022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>754341</t>
+          <t>756066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811504</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1402351</t>
+          <t>1399360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481077</t>
+          <t>1479478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1119083</t>
+          <t>1118666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1234664</t>
+          <t>1233119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>870508</t>
+          <t>869521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>975209</t>
+          <t>974405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2015020</t>
+          <t>2015671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2174439</t>
+          <t>2174376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2157750</t>
+          <t>2159295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2273331</t>
+          <t>2273748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2563894</t>
+          <t>2564698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2668595</t>
+          <t>2669582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4757078</t>
+          <t>4757141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4916497</t>
+          <t>4915846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156092</t>
+          <t>154487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204343</t>
+          <t>204897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105781</t>
+          <t>106760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141166</t>
+          <t>140033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271121</t>
+          <t>273434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330912</t>
+          <t>331091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430069</t>
+          <t>429515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>478320</t>
+          <t>479925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>534586</t>
+          <t>535719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>569971</t>
+          <t>568992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>979252</t>
+          <t>979073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1039043</t>
+          <t>1036730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125353</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310683</t>
+          <t>311969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158536</t>
+          <t>159841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203394</t>
+          <t>205444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>294979</t>
+          <t>278951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>486500</t>
+          <t>484235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>881178</t>
+          <t>879892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1066508</t>
+          <t>1088190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>754712</t>
+          <t>752662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>799570</t>
+          <t>798265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1663467</t>
+          <t>1665732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1854988</t>
+          <t>1871016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173654</t>
+          <t>173780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>234679</t>
+          <t>235038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85631</t>
+          <t>77029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209688</t>
+          <t>209221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235844</t>
+          <t>226181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>420404</t>
+          <t>424162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469837</t>
+          <t>469478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530862</t>
+          <t>530736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>723678</t>
+          <t>724145</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>847735</t>
+          <t>856337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1217477</t>
+          <t>1213719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1402037</t>
+          <t>1411700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190046</t>
+          <t>191752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247643</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154643</t>
+          <t>153356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219796</t>
+          <t>219540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360864</t>
+          <t>359160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>451287</t>
+          <t>448809</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>679188</t>
+          <t>680598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>736785</t>
+          <t>735079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871230</t>
+          <t>871486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936383</t>
+          <t>937670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1566571</t>
+          <t>1569049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1656994</t>
+          <t>1658698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>665502</t>
+          <t>659122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>926490</t>
+          <t>919495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>525297</t>
+          <t>541235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>713537</t>
+          <t>718797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1287875</t>
+          <t>1274431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1605712</t>
+          <t>1605487</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2531130</t>
+          <t>2538125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2792118</t>
+          <t>2798498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2944714</t>
+          <t>2939454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3132954</t>
+          <t>3117016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5510159</t>
+          <t>5510384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5827996</t>
+          <t>5841440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274201</t>
+          <t>275419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331213</t>
+          <t>326549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137479</t>
+          <t>139435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>182015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426574</t>
+          <t>425250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>494209</t>
+          <t>495737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362799</t>
+          <t>367463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419811</t>
+          <t>418593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>506687</t>
+          <t>506336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550872</t>
+          <t>548916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>888154</t>
+          <t>886626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>955789</t>
+          <t>957113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>353568</t>
+          <t>352541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>417826</t>
+          <t>412999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195716</t>
+          <t>194030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249589</t>
+          <t>246244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>569447</t>
+          <t>566932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>652858</t>
+          <t>650349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>542932</t>
+          <t>547759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>607190</t>
+          <t>608217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718804</t>
+          <t>722149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>772677</t>
+          <t>774363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1276293</t>
+          <t>1278802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359704</t>
+          <t>1362219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221083</t>
+          <t>219521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272965</t>
+          <t>273651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142014</t>
+          <t>142993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186162</t>
+          <t>187523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376414</t>
+          <t>373756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443487</t>
+          <t>443332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405544</t>
+          <t>404858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457426</t>
+          <t>458988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497679</t>
+          <t>496318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541827</t>
+          <t>540848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>918863</t>
+          <t>919018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>985936</t>
+          <t>988594</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>341557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>403481</t>
+          <t>402447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257874</t>
+          <t>255066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316263</t>
+          <t>312989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>617821</t>
+          <t>616776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>702468</t>
+          <t>701247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>539775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596603</t>
+          <t>600665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>722349</t>
+          <t>725623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>780738</t>
+          <t>783546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1278366</t>
+          <t>1279587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1363013</t>
+          <t>1364058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1252736</t>
+          <t>1249910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1365380</t>
+          <t>1361442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>781070</t>
+          <t>782094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>876985</t>
+          <t>883362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2058038</t>
+          <t>2061715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2217789</t>
+          <t>2208510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1910121</t>
+          <t>1914059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2022765</t>
+          <t>2025591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2502212</t>
+          <t>2495835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2598127</t>
+          <t>2597103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4436909</t>
+          <t>4446188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4596660</t>
+          <t>4592983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233231</t>
+          <t>234972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286717</t>
+          <t>288879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139298</t>
+          <t>137762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185614</t>
+          <t>185351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385859</t>
+          <t>385324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>456953</t>
+          <t>455685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416752</t>
+          <t>414590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470238</t>
+          <t>468497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>511436</t>
+          <t>511699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>557752</t>
+          <t>559288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>943566</t>
+          <t>944834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1014660</t>
+          <t>1015195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,49%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>347623</t>
+          <t>349765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411421</t>
+          <t>413718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>258600</t>
+          <t>259323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318886</t>
+          <t>323274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>623267</t>
+          <t>626712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>712581</t>
+          <t>716316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>605497</t>
+          <t>603200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>669295</t>
+          <t>667153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>713298</t>
+          <t>708910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773584</t>
+          <t>772861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1336521</t>
+          <t>1332786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1425835</t>
+          <t>1422390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253889</t>
+          <t>254094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>307706</t>
+          <t>308245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195859</t>
+          <t>194619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248020</t>
+          <t>249467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462627</t>
+          <t>465288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>538756</t>
+          <t>543670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449917</t>
+          <t>449378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503734</t>
+          <t>503529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>528158</t>
+          <t>526711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580319</t>
+          <t>581559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>995045</t>
+          <t>990131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1071174</t>
+          <t>1068513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>311519</t>
+          <t>310726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373556</t>
+          <t>370657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>258001</t>
+          <t>257671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317420</t>
+          <t>316620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>586123</t>
+          <t>584666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>672261</t>
+          <t>668509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574183</t>
+          <t>577082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636220</t>
+          <t>637013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733495</t>
+          <t>734295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>792914</t>
+          <t>793244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1326393</t>
+          <t>1330145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1412531</t>
+          <t>1413988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1203028</t>
+          <t>1207570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1319774</t>
+          <t>1324861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>905512</t>
+          <t>901501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1012153</t>
+          <t>1014393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2142650</t>
+          <t>2140869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2302854</t>
+          <t>2304193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2105975</t>
+          <t>2100888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2222721</t>
+          <t>2218179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2544174</t>
+          <t>2541934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2650815</t>
+          <t>2654826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4679222</t>
+          <t>4677883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4839426</t>
+          <t>4841207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226604</t>
+          <t>224999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274142</t>
+          <t>275259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146763</t>
+          <t>146148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192002</t>
+          <t>191320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381533</t>
+          <t>382396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>453962</t>
+          <t>453144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400658</t>
+          <t>399541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448196</t>
+          <t>449801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>479728</t>
+          <t>480410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>524967</t>
+          <t>525582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>892568</t>
+          <t>893386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>964997</t>
+          <t>964134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>304565</t>
+          <t>305033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366431</t>
+          <t>364371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244246</t>
+          <t>241982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300278</t>
+          <t>300105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>562462</t>
+          <t>564497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>646184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654928</t>
+          <t>656988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>716794</t>
+          <t>716326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>741707</t>
+          <t>741880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>797739</t>
+          <t>800003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1417468</t>
+          <t>1417160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1500882</t>
+          <t>1498847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278434</t>
+          <t>282319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>334659</t>
+          <t>339584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201555</t>
+          <t>199443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252319</t>
+          <t>249815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>497149</t>
+          <t>496042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576479</t>
+          <t>573219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>424029</t>
+          <t>419104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480254</t>
+          <t>476369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530576</t>
+          <t>533080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581340</t>
+          <t>583452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965103</t>
+          <t>968363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044433</t>
+          <t>1045540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>254293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314330</t>
+          <t>311049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>230295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286428</t>
+          <t>284468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>500583</t>
+          <t>498943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>580701</t>
+          <t>577694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>623237</t>
+          <t>626518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680022</t>
+          <t>683274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>756066</t>
+          <t>758026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1399360</t>
+          <t>1402367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1479478</t>
+          <t>1481118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1118666</t>
+          <t>1127117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1233119</t>
+          <t>1237940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>869521</t>
+          <t>869748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>974405</t>
+          <t>982473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2015671</t>
+          <t>2019716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2174376</t>
+          <t>2177719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2159295</t>
+          <t>2154474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2273748</t>
+          <t>2265297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2564698</t>
+          <t>2556630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2669582</t>
+          <t>2669355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4757141</t>
+          <t>4753798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4915846</t>
+          <t>4911801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -6569,22 +6569,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>192912</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154487</t>
+          <t>167906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204897</t>
+          <t>219871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>112918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140033</t>
+          <t>148620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>322804</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273434</t>
+          <t>293263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>358349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6682,27 +6682,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>456395</t>
+          <t>496716</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429515</t>
+          <t>469757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479925</t>
+          <t>521722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>553229</t>
+          <t>603221</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>535719</t>
+          <t>584493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568992</t>
+          <t>620195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1009624</t>
+          <t>1099937</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>979073</t>
+          <t>1064392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1036730</t>
+          <t>1129478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>238002</t>
+          <t>254952</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>223250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311969</t>
+          <t>286341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>180117</t>
+          <t>195819</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159841</t>
+          <t>173257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>222370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>418118</t>
+          <t>450771</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278951</t>
+          <t>411834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484235</t>
+          <t>489643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>953859</t>
+          <t>792824</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>879892</t>
+          <t>761435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1088190</t>
+          <t>824526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>777989</t>
+          <t>875019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752662</t>
+          <t>848468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>798265</t>
+          <t>897581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1731849</t>
+          <t>1667843</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1665732</t>
+          <t>1628971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1871016</t>
+          <t>1706780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>200999</t>
+          <t>214326</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173780</t>
+          <t>187196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235038</t>
+          <t>246765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77029</t>
+          <t>153266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209221</t>
+          <t>198519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>357112</t>
+          <t>388248</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226181</t>
+          <t>351999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424162</t>
+          <t>429674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>503517</t>
+          <t>587569</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469478</t>
+          <t>555130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530736</t>
+          <t>614699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>777253</t>
+          <t>638338</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>724145</t>
+          <t>613740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>856337</t>
+          <t>658993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1280769</t>
+          <t>1225906</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1213719</t>
+          <t>1184480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1411700</t>
+          <t>1262155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>217493</t>
+          <t>239558</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191752</t>
+          <t>210915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246233</t>
+          <t>270147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>193193</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153356</t>
+          <t>187111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219540</t>
+          <t>233878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>447140</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359160</t>
+          <t>411698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448809</t>
+          <t>485931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>709338</t>
+          <t>750504</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680598</t>
+          <t>719915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>735079</t>
+          <t>779147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>897833</t>
+          <t>907588</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871486</t>
+          <t>881292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>937670</t>
+          <t>928059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1607172</t>
+          <t>1658092</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1569049</t>
+          <t>1619301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1658698</t>
+          <t>1693534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>659122</t>
+          <t>847849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>919495</t>
+          <t>964672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>541235</t>
+          <t>666059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>718797</t>
+          <t>753555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1274431</t>
+          <t>1528923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1605487</t>
+          <t>1683254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2623110</t>
+          <t>2627613</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2538125</t>
+          <t>2564689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2798498</t>
+          <t>2681512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3006305</t>
+          <t>3024166</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2939454</t>
+          <t>2977825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3117016</t>
+          <t>3065321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5629414</t>
+          <t>5651778</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5510384</t>
+          <t>5577486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5841440</t>
+          <t>5731817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
